--- a/duoki_editor/resources/data/save/Speech_save.xlsx
+++ b/duoki_editor/resources/data/save/Speech_save.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\DuokiEditor\duoki_editor\resources\data\save\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393CB45E-A091-40C7-85F6-B8C531B99D89}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F00DCC-3BCE-4191-AD3A-48CDE3B4B568}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9555" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="115">
   <si>
     <t>id</t>
   </si>
@@ -373,90 +373,6 @@
   </si>
   <si>
     <t>没关系，我们去帮助他吧！{user_name} 老板，我们一起把魔法商店做的越来越好吧！</t>
-  </si>
-  <si>
-    <t>商店_限时找实体道具_0_1_通用_a5_e0</t>
-  </si>
-  <si>
-    <t>{user_name}，限时特卖会活动开始啦！</t>
-  </si>
-  <si>
-    <t>先把货架准备好吧！</t>
-  </si>
-  <si>
-    <t>货架摆在柜台上吧</t>
-  </si>
-  <si>
-    <t>200543|200521</t>
-  </si>
-  <si>
-    <t>time_out_task_1</t>
-  </si>
-  <si>
-    <t>现在要找的东西都是小卡片哦！预备！三、二、一，开始！</t>
-  </si>
-  <si>
-    <t>在实体道具里找哦！</t>
-  </si>
-  <si>
-    <t>min(10,3+level/5)</t>
-  </si>
-  <si>
-    <t>time_out_task_end</t>
-  </si>
-  <si>
-    <t>天呐！你卖出了好多东西呀！给你20个宝石！</t>
-  </si>
-  <si>
-    <t>这次卖的还不错呀！给你10个宝石！</t>
-  </si>
-  <si>
-    <t>卖的有点少哦！只能给你5个宝石！</t>
-  </si>
-  <si>
-    <t>下次要继续努力啦！这次一个宝石都没有哦！</t>
-  </si>
-  <si>
-    <t>20|10|5|0</t>
-  </si>
-  <si>
-    <t>清理下桌面吧！</t>
-  </si>
-  <si>
-    <t>商店_限时找地图道具_0_1_通用_a5_e0</t>
-  </si>
-  <si>
-    <t>我们来看看这次能卖出去多少东西吧！</t>
-  </si>
-  <si>
-    <t>time_out_task_2</t>
-  </si>
-  <si>
-    <t>这次要卖的东西都在地图上哦！准备好手指头吧！预备！三、二、一，开始！</t>
-  </si>
-  <si>
-    <t>在地图上里找哦！记得用手指头指出来！</t>
-  </si>
-  <si>
-    <t>商店_限时找混合道具_0_1_通用_a5_e0</t>
-  </si>
-  <si>
-    <t>time_out_task_3</t>
-  </si>
-  <si>
-    <t>现在要找的东西有可能是小卡片，也有可能是地图上的哦！预备！三、二、一，开始！</t>
-  </si>
-  <si>
-    <t>有的是实体道具，有的在地图上哦！</t>
-  </si>
-  <si>
-    <t>天呐！你卖出了好多东西呀！有这些，{words}给你20个宝石！</t>
-  </si>
-  <si>
-    <t>这次卖的还不错呀！有这些，{words}给你10个宝石！</t>
-  </si>
-  <si>
-    <t>卖的有点少哦！有这些，{words}只能给你5个宝石！</t>
   </si>
 </sst>
 </file>
@@ -2447,7 +2363,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60023430-3851-4D23-B419-54DD3EF10878}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.15">
@@ -2621,499 +2537,6 @@
         <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A7">
-        <v>40005</v>
-      </c>
-      <c r="B7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A8">
-        <v>40006</v>
-      </c>
-      <c r="B8" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>117</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A9">
-        <v>40007</v>
-      </c>
-      <c r="B9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" t="s">
-        <v>118</v>
-      </c>
-      <c r="G9" t="s">
-        <v>118</v>
-      </c>
-      <c r="H9" t="s">
-        <v>119</v>
-      </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A10">
-        <v>40008</v>
-      </c>
-      <c r="B10" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" t="s">
-        <v>120</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F10" t="s">
-        <v>122</v>
-      </c>
-      <c r="G10" t="s">
-        <v>123</v>
-      </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A11">
-        <v>40009</v>
-      </c>
-      <c r="B11" t="s">
-        <v>115</v>
-      </c>
-      <c r="C11" t="s">
-        <v>124</v>
-      </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>125</v>
-      </c>
-      <c r="F11" t="s">
-        <v>126</v>
-      </c>
-      <c r="G11" t="s">
-        <v>127</v>
-      </c>
-      <c r="H11" t="s">
-        <v>128</v>
-      </c>
-      <c r="I11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A12">
-        <v>40010</v>
-      </c>
-      <c r="B12" t="s">
-        <v>115</v>
-      </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" t="s">
-        <v>130</v>
-      </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A13">
-        <v>40011</v>
-      </c>
-      <c r="B13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>116</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A14">
-        <v>40012</v>
-      </c>
-      <c r="B14" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" t="s">
-        <v>132</v>
-      </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A15">
-        <v>40013</v>
-      </c>
-      <c r="B15" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15" t="s">
-        <v>133</v>
-      </c>
-      <c r="D15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" t="s">
-        <v>134</v>
-      </c>
-      <c r="F15" t="s">
-        <v>135</v>
-      </c>
-      <c r="G15" t="s">
-        <v>123</v>
-      </c>
-      <c r="H15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A16">
-        <v>40014</v>
-      </c>
-      <c r="B16" t="s">
-        <v>131</v>
-      </c>
-      <c r="C16" t="s">
-        <v>124</v>
-      </c>
-      <c r="D16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" t="s">
-        <v>125</v>
-      </c>
-      <c r="F16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G16" t="s">
-        <v>127</v>
-      </c>
-      <c r="H16" t="s">
-        <v>128</v>
-      </c>
-      <c r="I16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A17">
-        <v>40015</v>
-      </c>
-      <c r="B17" t="s">
-        <v>131</v>
-      </c>
-      <c r="C17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" t="s">
-        <v>130</v>
-      </c>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A18">
-        <v>40016</v>
-      </c>
-      <c r="B18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" t="s">
-        <v>116</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A19">
-        <v>40017</v>
-      </c>
-      <c r="B19" t="s">
-        <v>136</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" t="s">
-        <v>117</v>
-      </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A20">
-        <v>40018</v>
-      </c>
-      <c r="B20" t="s">
-        <v>136</v>
-      </c>
-      <c r="C20" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" t="s">
-        <v>118</v>
-      </c>
-      <c r="F20" t="s">
-        <v>118</v>
-      </c>
-      <c r="G20" t="s">
-        <v>118</v>
-      </c>
-      <c r="H20" t="s">
-        <v>119</v>
-      </c>
-      <c r="I20" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A21">
-        <v>40019</v>
-      </c>
-      <c r="B21" t="s">
-        <v>136</v>
-      </c>
-      <c r="C21" t="s">
-        <v>137</v>
-      </c>
-      <c r="D21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" t="s">
-        <v>138</v>
-      </c>
-      <c r="F21" t="s">
-        <v>139</v>
-      </c>
-      <c r="G21" t="s">
-        <v>123</v>
-      </c>
-      <c r="H21" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A22">
-        <v>40020</v>
-      </c>
-      <c r="B22" t="s">
-        <v>136</v>
-      </c>
-      <c r="C22" t="s">
-        <v>124</v>
-      </c>
-      <c r="D22" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" t="s">
-        <v>140</v>
-      </c>
-      <c r="F22" t="s">
-        <v>141</v>
-      </c>
-      <c r="G22" t="s">
-        <v>142</v>
-      </c>
-      <c r="H22" t="s">
-        <v>128</v>
-      </c>
-      <c r="I22" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A23">
-        <v>40021</v>
-      </c>
-      <c r="B23" t="s">
-        <v>136</v>
-      </c>
-      <c r="C23" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" t="s">
-        <v>130</v>
-      </c>
-      <c r="F23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" t="s">
         <v>15</v>
       </c>
     </row>
